--- a/data/employees/EMP075/AST-EMP075-06.xlsx
+++ b/data/employees/EMP075/AST-EMP075-06.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Resource Utilization" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,36 +26,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00048A81"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -69,17 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,166 +414,1883 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>System Resource Utilization - Casey Lee (IT)</t>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>EmployeeId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Narrative</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Author: Casey Lee | Role: Lead | Location: Portland | Date: 2025-03-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ast Emp075 06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>69</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ast Emp075 06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>84</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Server</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>CPU %</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Memory %</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Disk %</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Network (Mbps)</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Status</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ast Emp075 06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>84</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PROD-APP-01</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>42</v>
-      </c>
-      <c r="C5" t="n">
-        <v>67</v>
-      </c>
-      <c r="D5" t="n">
-        <v>55</v>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ast Emp075 06</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-W04</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
       </c>
       <c r="E5" t="n">
-        <v>1200</v>
+        <v>94</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Section 1: Quarterly delivery milestones. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PROD-SQL-02</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>58</v>
-      </c>
-      <c r="C6" t="n">
-        <v>81</v>
-      </c>
-      <c r="D6" t="n">
-        <v>88</v>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ast Emp075 06</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-W05</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
       </c>
       <c r="E6" t="n">
-        <v>880</v>
+        <v>61</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>WARNING</t>
+          <t>Section 1: Fabric semantic model planning. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DEV-WEB-01</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>15</v>
-      </c>
-      <c r="C7" t="n">
-        <v>34</v>
-      </c>
-      <c r="D7" t="n">
-        <v>40</v>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ast Emp075 06</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-W06</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
       </c>
       <c r="E7" t="n">
-        <v>200</v>
+        <v>82</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Section 1: Fabric semantic model planning. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TEST-API-01</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>28</v>
-      </c>
-      <c r="C8" t="n">
-        <v>52</v>
-      </c>
-      <c r="D8" t="n">
-        <v>62</v>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ast Emp075 06</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-W07</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
       </c>
       <c r="E8" t="n">
-        <v>450</v>
+        <v>89</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Section 1: Quarterly delivery milestones. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ast Emp075 06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-W08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>97</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ast Emp075 06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>94</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ast Emp075 06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>71</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ast Emp075 06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>95</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ast Emp075 06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>64</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ast Emp075 06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>63</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ast Emp075 06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>89</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ast Emp075 06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>93</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ast Emp075 06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>69</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ast Emp075 06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>68</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ast Emp075 06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>82</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ast Emp075 06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>76</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ast Emp075 06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>96</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ast Emp075 06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>90</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ast Emp075 06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>71</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ast Emp075 06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>81</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ast Emp075 06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>98</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EMP075</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP075 contributes to ast emp075 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>